--- a/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/anova_taxa.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>174.17</v>
+        <v>343.6</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>226.85</v>
+        <v>28.32</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>21.11</v>
+        <v>303.28</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.85 ± 0.77</t>
+          <t>0.35 ± 0.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.56 ± 0.45</t>
+          <t>6.07 ± 0.12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.15 ± 0.08</t>
+          <t>0.23 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>101.15</v>
+        <v>173.27</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>207.47</v>
+        <v>101.88</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>13.41</v>
+        <v>42.52</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.87 ± 0.59</t>
+          <t>3.04 ± 0.41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.09 ± 0.43</t>
+          <t>1.41 ± 0.40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.31 ± 0.30</t>
+          <t>5.95 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -580,38 +580,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>61.36</v>
+        <v>88.13</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>186.44</v>
+        <v>130.69</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>9.050000000000001</v>
+        <v>16.86</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0004***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.22 ± 0.59</t>
+          <t>5.35 ± 0.30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.86 ± 0.35</t>
+          <t>2.11 ± 0.55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4.24 ± 0.39</t>
+          <t>3.98 ± 0.34</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.71</v>
+        <v>35.94</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>67.5</v>
+        <v>164.3</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>7.22</v>
+        <v>5.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0016**</t>
+          <t>0.0071**</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>3.07 ± 0.46</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.18 ± 0.12</t>
+          <t>1.03 ± 0.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.29 ± 0.41</t>
+          <t>1.94 ± 0.40</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.05</v>
+        <v>29.15</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>188.02</v>
+        <v>133.57</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>3.96</v>
+        <v>5.45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0248*</t>
+          <t>0.0072**</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.80 ± 0.43</t>
+          <t>0.83 ± 0.33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.51 ± 0.41</t>
+          <t>2.51 ± 0.59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.31 ± 0.38</t>
+          <t>0.82 ± 0.28</t>
         </is>
       </c>
     </row>
@@ -711,42 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.38</v>
+        <v>1.81</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>158.87</v>
+        <v>14.49</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0493*</t>
+          <t>0.0530.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.34 ± 0.55</t>
+          <t>0.11 ± 0.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.07 ± 0.35</t>
+          <t>0.52 ± 0.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.91 ± 0.32</t>
+          <t>0.09 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -766,32 +766,32 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>21.88</v>
+        <v>17.75</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0860.</t>
+          <t>0.0655.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.06 ± 0.06</t>
+          <t>0.06 ± 0.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.03 ± 0.03</t>
+          <t>0.52 ± 0.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.44 ± 0.25</t>
+          <t>0.08 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.48</v>
+        <v>3.92</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>16.89</v>
+        <v>42.21</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0999.</t>
+          <t>0.1089</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.43 ± 0.19</t>
+          <t>0.11 ± 0.11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.07 ± 0.05</t>
+          <t>0.23 ± 0.16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.36 ± 0.17</t>
+          <t>0.72 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.67</v>
+        <v>1.71</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>45.8</v>
+        <v>19.05</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1167</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>0.04 ± 0.04</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.63 ± 0.25</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.29 ± 0.11</t>
+          <t>0.40 ± 0.25</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.15</v>
+        <v>6.81</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>17.82</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.1792</t>
+          <t>0.1211</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.48 ± 0.25</t>
+          <t>0.56 ± 0.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.19 ± 0.10</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.10 ± 0.07</t>
+          <t>0.93 ± 0.37</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.41</v>
+        <v>2.16</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>6.4</v>
+        <v>27.56</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.1817</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.51 ± 0.21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.02 ± 0.02</t>
+          <t>0.08 ± 0.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.19 ± 0.13</t>
+          <t>0.56 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -985,38 +985,38 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.31</v>
+        <v>2.32</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>61.61</v>
+        <v>49.67</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.2370</t>
+          <t>0.3192</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.62 ± 0.30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.61 ± 0.26</t>
+          <t>0.13 ± 0.10</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.49 ± 0.22</t>
+          <t>0.26 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -1030,38 +1030,38 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.3606</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>0.08 ± 0.06</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.06 ± 0.05</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.16 ± 0.11</t>
+          <t>0.17 ± 0.12</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.87</v>
+        <v>0.15</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>29.63</v>
+        <v>3.82</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.4524</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.20 ± 0.20</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.36 ± 0.15</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.53 ± 0.15</t>
+          <t>0.11 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>45.84</v>
+        <v>17.37</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>0.52</v>
+        <v>0.95</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.5976</t>
+          <t>0.3929</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.37 ± 0.25</t>
+          <t>0.13 ± 0.10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.21 ± 0.12</t>
+          <t>0.38 ± 0.17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.48 ± 0.28</t>
+          <t>0.34 ± 0.16</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>21.07</v>
+        <v>41.15</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.7388</t>
+          <t>0.8291</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.21 ± 0.21</t>
+          <t>0.41 ± 0.27</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.27 ± 0.14</t>
+          <t>0.26 ± 0.19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.12 ± 0.07</t>
+          <t>0.26 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
